--- a/templates/INFRA ADV - template.xlsx
+++ b/templates/INFRA ADV - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$7</definedName>
@@ -1364,96 +1364,96 @@
     <row r="13" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>113.28838513</v>
+        <v>113.55693486</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>0.0002729645120822521</v>
+        <v>0.0007376102336413837</v>
       </c>
       <c r="E13" s="35" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>0.5030098497205824</v>
+        <v>1.359243404741622</v>
       </c>
     </row>
     <row r="14" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C14" s="38" t="n">
-        <v>113.25746986</v>
+        <v>113.47323584</v>
       </c>
       <c r="D14" s="39" t="n">
-        <v>-1.13036740990724e-05</v>
+        <v>0.0003332000147682201</v>
       </c>
       <c r="E14" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>-0.02083003159088876</v>
+        <v>0.6140098142316559</v>
       </c>
     </row>
     <row r="15" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C15" s="38" t="n">
-        <v>113.2587501</v>
+        <v>113.43543915</v>
       </c>
       <c r="D15" s="39" t="n">
-        <v>0.0004713945336614067</v>
+        <v>0.0002005313402460018</v>
       </c>
       <c r="E15" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>0.8686700396595078</v>
+        <v>0.3695324295160153</v>
       </c>
     </row>
     <row r="16" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C16" s="38" t="n">
-        <v>113.2053857</v>
+        <v>113.41269635</v>
       </c>
       <c r="D16" s="39" t="n">
-        <v>-9.767635851232193e-05</v>
+        <v>-5.231336349043048e-05</v>
       </c>
       <c r="E16" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>-0.1799947181475804</v>
+        <v>-0.09640131204956935</v>
       </c>
     </row>
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C17" s="38" t="n">
-        <v>113.21644427</v>
+        <v>113.41862966</v>
       </c>
       <c r="D17" s="39" t="n">
-        <v>0.001389585786699454</v>
+        <v>0.000733792728151661</v>
       </c>
       <c r="E17" s="39" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>2.560682091637349</v>
+        <v>1.352208633635134</v>
       </c>
     </row>
     <row r="18" ht="15.95" customHeight="1">
@@ -1493,18 +1493,18 @@
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="32">
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C20" s="41" t="inlineStr"/>
       <c r="D20" s="35" t="n">
-        <v>0.008982934337462778</v>
+        <v>0.002017628777846836</v>
       </c>
       <c r="E20" s="35" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.8568748893768706</v>
+        <v>0.5302814497145035</v>
       </c>
       <c r="G20" s="42" t="n"/>
     </row>
@@ -1517,13 +1517,13 @@
       </c>
       <c r="C21" s="49" t="inlineStr"/>
       <c r="D21" s="39" t="n">
-        <v>0.0110507952819241</v>
+        <v>0.006829279030328372</v>
       </c>
       <c r="E21" s="39" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>0.9528309521239068</v>
+        <v>0.5933127143775004</v>
       </c>
       <c r="G21" s="50" t="n"/>
     </row>
@@ -1536,13 +1536,13 @@
       </c>
       <c r="C22" s="49" t="inlineStr"/>
       <c r="D22" s="39" t="n">
-        <v>0.03532238567599988</v>
+        <v>0.03242248996930353</v>
       </c>
       <c r="E22" s="39" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1.000970521942544</v>
+        <v>0.9211286368592708</v>
       </c>
       <c r="G22" s="50" t="n"/>
     </row>
@@ -1555,13 +1555,13 @@
       </c>
       <c r="C23" s="49" t="inlineStr"/>
       <c r="D23" s="39" t="n">
-        <v>0.07906594293834446</v>
+        <v>0.07367353954831923</v>
       </c>
       <c r="E23" s="39" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1.10015732924025</v>
+        <v>1.026448298162773</v>
       </c>
       <c r="G23" s="50" t="n"/>
     </row>
@@ -1574,13 +1574,13 @@
       </c>
       <c r="C24" s="49" t="inlineStr"/>
       <c r="D24" s="39" t="n">
-        <v>0.03217063195829173</v>
+        <v>0.03461738891584099</v>
       </c>
       <c r="E24" s="39" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F24" s="40" t="n">
-        <v>0.9917262328418425</v>
+        <v>0.909658109537503</v>
       </c>
       <c r="G24" s="50" t="n"/>
     </row>
@@ -1612,13 +1612,13 @@
       </c>
       <c r="C26" s="49" t="inlineStr"/>
       <c r="D26" s="39" t="n">
-        <v>0.1328838512999999</v>
+        <v>0.1355693486</v>
       </c>
       <c r="E26" s="39" t="n">
-        <v>0.1134063390652134</v>
+        <v>0.1194631520887273</v>
       </c>
       <c r="F26" s="40" t="n">
-        <v>1.171749766329959</v>
+        <v>1.134821459417967</v>
       </c>
       <c r="G26" s="50" t="n"/>
     </row>
@@ -1646,7 +1646,7 @@
       <c r="C29" s="12" t="n"/>
       <c r="D29" s="12" t="n"/>
       <c r="E29" s="43" t="n">
-        <v>284225512.81</v>
+        <v>281045252.39</v>
       </c>
       <c r="F29" s="27" t="n"/>
       <c r="G29" s="3" t="n"/>
@@ -1661,7 +1661,7 @@
       <c r="C30" s="12" t="n"/>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="43" t="n">
-        <v>266332623.2240816</v>
+        <v>267085389.6033496</v>
       </c>
       <c r="F30" s="27" t="n"/>
       <c r="G30" s="3" t="n"/>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D32" s="18" t="n"/>
